--- a/Voltage_discharge.xlsx
+++ b/Voltage_discharge.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="30" windowWidth="15960" windowHeight="13170" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="30" windowWidth="15960" windowHeight="12220" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -145,8 +145,17 @@
     <t>Dual Axis</t>
   </si>
   <si>
+    <t>Single Axis</t>
+  </si>
+  <si>
+    <t>AVERAGES</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
     <r>
-      <t>Fixed at 29</t>
+      <t>Fixed at 34</t>
     </r>
     <r>
       <rPr>
@@ -156,15 +165,6 @@
       </rPr>
       <t xml:space="preserve"> Degrees</t>
     </r>
-  </si>
-  <si>
-    <t>Single Axis</t>
-  </si>
-  <si>
-    <t>AVERAGES</t>
-  </si>
-  <si>
-    <t>SUM</t>
   </si>
 </sst>
 </file>
@@ -606,7 +606,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999842"/>
+          <c:h val="0.81033699999999831"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1879,11 +1879,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="111181824"/>
-        <c:axId val="111184896"/>
+        <c:axId val="129728896"/>
+        <c:axId val="129731968"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="111181824"/>
+        <c:axId val="129728896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1915,14 +1915,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="111184896"/>
+        <c:crossAx val="129731968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="111184896"/>
+        <c:axId val="129731968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -1965,7 +1965,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="111181824"/>
+        <c:crossAx val="129728896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -1989,7 +1989,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000198E-2"/>
+          <c:h val="6.4066700000000212E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -2029,7 +2029,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000144" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000144" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2049,7 +2049,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999842"/>
+          <c:h val="0.81033699999999831"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -3488,11 +3488,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="110822144"/>
-        <c:axId val="110823680"/>
+        <c:axId val="129538304"/>
+        <c:axId val="129544192"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="110822144"/>
+        <c:axId val="129538304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3524,14 +3524,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110823680"/>
+        <c:crossAx val="129544192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="110823680"/>
+        <c:axId val="129544192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -3574,7 +3574,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110822144"/>
+        <c:crossAx val="129538304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -3598,7 +3598,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000198E-2"/>
+          <c:h val="6.4066700000000212E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -3638,7 +3638,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000144" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000144" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -3655,10 +3655,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.1082900000000008E-2"/>
+          <c:x val="9.1082899999999994E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89393599999999951"/>
-          <c:h val="0.81033699999999842"/>
+          <c:h val="0.81033699999999831"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -4600,11 +4600,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="110880640"/>
-        <c:axId val="110882176"/>
+        <c:axId val="129682816"/>
+        <c:axId val="129684608"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="110880640"/>
+        <c:axId val="129682816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4636,14 +4636,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110882176"/>
+        <c:crossAx val="129684608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="3"/>
         <c:minorUnit val="1.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="110882176"/>
+        <c:axId val="129684608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -4685,7 +4685,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110880640"/>
+        <c:crossAx val="129682816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -4709,7 +4709,7 @@
           <c:x val="7.5226400000000082E-2"/>
           <c:y val="0"/>
           <c:w val="0.88994100000000065"/>
-          <c:h val="6.4066700000000198E-2"/>
+          <c:h val="6.4066700000000212E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -4749,7 +4749,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000144" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000144" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -4769,7 +4769,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999842"/>
+          <c:h val="0.81033699999999831"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6042,11 +6042,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="110960000"/>
-        <c:axId val="110974080"/>
+        <c:axId val="129725568"/>
+        <c:axId val="129727104"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="110960000"/>
+        <c:axId val="129725568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6078,14 +6078,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110974080"/>
+        <c:crossAx val="129727104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="110974080"/>
+        <c:axId val="129727104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -6128,7 +6128,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110960000"/>
+        <c:crossAx val="129725568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -6188,7 +6188,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000198E-2"/>
+          <c:h val="6.4066700000000212E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -6232,7 +6232,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000144" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000144" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -6249,10 +6249,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.4312400000000269E-2"/>
+          <c:x val="6.4312400000000297E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.88765000000000005"/>
-          <c:h val="0.81033699999999842"/>
+          <c:h val="0.81033699999999831"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6460,11 +6460,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="110998272"/>
-        <c:axId val="110999808"/>
+        <c:axId val="129903616"/>
+        <c:axId val="129909504"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="110998272"/>
+        <c:axId val="129903616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="806395000"/>
@@ -6497,12 +6497,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110999808"/>
+        <c:crossAx val="129909504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="110999808"/>
+        <c:axId val="129909504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6543,7 +6543,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="110998272"/>
+        <c:crossAx val="129903616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.2"/>
@@ -6567,7 +6567,7 @@
           <c:x val="4.0081200000000004E-2"/>
           <c:y val="0"/>
           <c:w val="0.9"/>
-          <c:h val="6.4066700000000198E-2"/>
+          <c:h val="6.4066700000000212E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -6607,7 +6607,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000144" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000144" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -6624,17 +6624,41 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>Current Production</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t> over Time</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -6653,7 +6677,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Fixed at 29 Degrees</c:v>
+                  <c:v>Fixed at 34 Degrees</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7221,11 +7245,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="111204224"/>
-        <c:axId val="111205760"/>
+        <c:axId val="130158976"/>
+        <c:axId val="130160512"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="111204224"/>
+        <c:axId val="130158976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7233,14 +7257,30 @@
         <c:numFmt formatCode="h:mm\ AM/PM" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="111205760"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="130160512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="111205760"/>
+        <c:axId val="130160512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7253,10 +7293,22 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t>Solar Current (A)</a:t>
                 </a:r>
               </a:p>
@@ -7267,20 +7319,62 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="111204224"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="130158976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx1"/>
+    </a:solidFill>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.750000000000001" l="0.70000000000000062" r="0.70000000000000062" t="0.750000000000001" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000111" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000111" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -8532,7 +8626,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="33.5703125" customWidth="1"/>
+    <col min="2" max="4" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="49.9" customHeight="1">
@@ -8542,7 +8636,7 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
     </row>
-    <row r="7" spans="2:4" ht="18">
+    <row r="7" spans="2:4" ht="17.5">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -8553,14 +8647,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15">
+    <row r="9" spans="2:4" ht="15.5">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="30">
+    <row r="10" spans="2:4" ht="31">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -8569,14 +8663,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15">
+    <row r="11" spans="2:4" ht="15.5">
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="30">
+    <row r="12" spans="2:4" ht="31">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -8585,14 +8679,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="15">
+    <row r="13" spans="2:4" ht="15.5">
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" ht="30">
+    <row r="14" spans="2:4" ht="31">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>16</v>
@@ -8601,14 +8695,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="15">
+    <row r="15" spans="2:4" ht="15.5">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" ht="30">
+    <row r="16" spans="2:4" ht="31">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>26</v>
@@ -8634,10 +8728,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I263"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="19.899999999999999" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
-    <col min="1" max="10" width="16.28515625" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="16.28515625" style="5"/>
+    <col min="1" max="10" width="16.26953125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="16.26953125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
@@ -8699,7 +8793,7 @@
       </c>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="15">
@@ -8722,7 +8816,7 @@
       </c>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="15">
@@ -8745,7 +8839,7 @@
       </c>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="13"/>
       <c r="B6" s="14"/>
       <c r="C6" s="15">
@@ -8768,7 +8862,7 @@
       </c>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="13"/>
       <c r="B7" s="14"/>
       <c r="C7" s="15">
@@ -8791,7 +8885,7 @@
       </c>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="15">
@@ -8814,7 +8908,7 @@
       </c>
       <c r="I8" s="16"/>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="15">
@@ -8837,7 +8931,7 @@
       </c>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="14"/>
       <c r="C10" s="15">
@@ -8860,7 +8954,7 @@
       </c>
       <c r="I10" s="16"/>
     </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="15">
@@ -8883,7 +8977,7 @@
       </c>
       <c r="I11" s="16"/>
     </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="15">
@@ -8906,7 +9000,7 @@
       </c>
       <c r="I12" s="16"/>
     </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="15">
@@ -8929,7 +9023,7 @@
       </c>
       <c r="I13" s="16"/>
     </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="15">
@@ -8952,7 +9046,7 @@
       </c>
       <c r="I14" s="16"/>
     </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="15">
@@ -8975,7 +9069,7 @@
       </c>
       <c r="I15" s="16"/>
     </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="15">
@@ -8998,7 +9092,7 @@
       </c>
       <c r="I16" s="16"/>
     </row>
-    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="15">
@@ -9021,7 +9115,7 @@
       </c>
       <c r="I17" s="16"/>
     </row>
-    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="15">
@@ -9044,7 +9138,7 @@
       </c>
       <c r="I18" s="16"/>
     </row>
-    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="15">
@@ -9067,7 +9161,7 @@
       </c>
       <c r="I19" s="16"/>
     </row>
-    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="15">
@@ -9090,7 +9184,7 @@
       </c>
       <c r="I20" s="16"/>
     </row>
-    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="15">
@@ -9113,7 +9207,7 @@
       </c>
       <c r="I21" s="16"/>
     </row>
-    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="15">
@@ -9136,7 +9230,7 @@
       </c>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="15">
@@ -9155,7 +9249,7 @@
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
     </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="15">
@@ -9174,7 +9268,7 @@
       <c r="H24" s="16"/>
       <c r="I24" s="16"/>
     </row>
-    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="15">
@@ -9193,7 +9287,7 @@
       <c r="H25" s="16"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="15">
@@ -9212,7 +9306,7 @@
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
     </row>
-    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="15">
@@ -9231,7 +9325,7 @@
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
     </row>
-    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15">
@@ -9250,7 +9344,7 @@
       <c r="H28" s="16"/>
       <c r="I28" s="16"/>
     </row>
-    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="15">
@@ -9269,7 +9363,7 @@
       <c r="H29" s="16"/>
       <c r="I29" s="16"/>
     </row>
-    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="15">
@@ -9288,7 +9382,7 @@
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
     </row>
-    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="15">
@@ -9307,7 +9401,7 @@
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
     </row>
-    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="15">
@@ -9326,7 +9420,7 @@
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
     </row>
-    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="15">
@@ -9345,7 +9439,7 @@
       <c r="H33" s="16"/>
       <c r="I33" s="16"/>
     </row>
-    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="15">
@@ -9364,7 +9458,7 @@
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
     </row>
-    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="35" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="15">
@@ -9383,7 +9477,7 @@
       <c r="H35" s="16"/>
       <c r="I35" s="16"/>
     </row>
-    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="15">
@@ -9402,7 +9496,7 @@
       <c r="H36" s="16"/>
       <c r="I36" s="16"/>
     </row>
-    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="15">
@@ -9421,7 +9515,7 @@
       <c r="H37" s="16"/>
       <c r="I37" s="16"/>
     </row>
-    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="15">
@@ -9440,7 +9534,7 @@
       <c r="H38" s="16"/>
       <c r="I38" s="16"/>
     </row>
-    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="15">
@@ -9459,7 +9553,7 @@
       <c r="H39" s="16"/>
       <c r="I39" s="16"/>
     </row>
-    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="15">
@@ -9478,7 +9572,7 @@
       <c r="H40" s="16"/>
       <c r="I40" s="16"/>
     </row>
-    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="41" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="15">
@@ -9497,7 +9591,7 @@
       <c r="H41" s="16"/>
       <c r="I41" s="16"/>
     </row>
-    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="42" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="15">
@@ -9516,7 +9610,7 @@
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
     </row>
-    <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="15">
@@ -9535,7 +9629,7 @@
       <c r="H43" s="16"/>
       <c r="I43" s="16"/>
     </row>
-    <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="44" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="15">
@@ -9554,7 +9648,7 @@
       <c r="H44" s="16"/>
       <c r="I44" s="16"/>
     </row>
-    <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="45" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="15">
@@ -9573,7 +9667,7 @@
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
     </row>
-    <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="46" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="15">
@@ -9592,7 +9686,7 @@
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
     </row>
-    <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="47" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="15">
@@ -9611,7 +9705,7 @@
       <c r="H47" s="16"/>
       <c r="I47" s="16"/>
     </row>
-    <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="48" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="15">
@@ -9630,7 +9724,7 @@
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
     </row>
-    <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="49" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="15">
@@ -9649,7 +9743,7 @@
       <c r="H49" s="16"/>
       <c r="I49" s="16"/>
     </row>
-    <row r="50" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="50" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="15">
@@ -9668,7 +9762,7 @@
       <c r="H50" s="16"/>
       <c r="I50" s="16"/>
     </row>
-    <row r="51" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="51" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="15">
@@ -9687,7 +9781,7 @@
       <c r="H51" s="16"/>
       <c r="I51" s="16"/>
     </row>
-    <row r="52" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="15">
@@ -9706,7 +9800,7 @@
       <c r="H52" s="16"/>
       <c r="I52" s="16"/>
     </row>
-    <row r="53" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="53" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="15">
@@ -9725,7 +9819,7 @@
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
     </row>
-    <row r="54" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="54" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="15">
@@ -9744,7 +9838,7 @@
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
     </row>
-    <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="55" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="15">
@@ -9763,7 +9857,7 @@
       <c r="H55" s="16"/>
       <c r="I55" s="16"/>
     </row>
-    <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="56" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="15">
@@ -9782,7 +9876,7 @@
       <c r="H56" s="16"/>
       <c r="I56" s="16"/>
     </row>
-    <row r="57" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="15">
@@ -9801,7 +9895,7 @@
       <c r="H57" s="16"/>
       <c r="I57" s="16"/>
     </row>
-    <row r="58" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="58" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="15">
@@ -9820,7 +9914,7 @@
       <c r="H58" s="16"/>
       <c r="I58" s="16"/>
     </row>
-    <row r="59" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="59" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="15">
@@ -9839,7 +9933,7 @@
       <c r="H59" s="16"/>
       <c r="I59" s="16"/>
     </row>
-    <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="15">
@@ -9858,7 +9952,7 @@
       <c r="H60" s="16"/>
       <c r="I60" s="16"/>
     </row>
-    <row r="61" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="15">
@@ -9877,7 +9971,7 @@
       <c r="H61" s="16"/>
       <c r="I61" s="16"/>
     </row>
-    <row r="62" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="62" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="15">
@@ -9896,7 +9990,7 @@
       <c r="H62" s="16"/>
       <c r="I62" s="16"/>
     </row>
-    <row r="63" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="15">
@@ -9915,7 +10009,7 @@
       <c r="H63" s="16"/>
       <c r="I63" s="16"/>
     </row>
-    <row r="64" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="64" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="15">
@@ -9934,7 +10028,7 @@
       <c r="H64" s="16"/>
       <c r="I64" s="16"/>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="65" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="15">
@@ -9953,7 +10047,7 @@
       <c r="H65" s="16"/>
       <c r="I65" s="16"/>
     </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="66" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="15">
@@ -9972,7 +10066,7 @@
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
     </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="15">
@@ -9991,7 +10085,7 @@
       <c r="H67" s="16"/>
       <c r="I67" s="16"/>
     </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="15">
@@ -10010,7 +10104,7 @@
       <c r="H68" s="16"/>
       <c r="I68" s="16"/>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="69" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="15">
@@ -10029,7 +10123,7 @@
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="70" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="15">
@@ -10048,7 +10142,7 @@
       <c r="H70" s="16"/>
       <c r="I70" s="16"/>
     </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="71" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="15">
@@ -10067,7 +10161,7 @@
       <c r="H71" s="16"/>
       <c r="I71" s="16"/>
     </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="72" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="15">
@@ -10086,7 +10180,7 @@
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
     </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="73" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="15">
@@ -10105,7 +10199,7 @@
       <c r="H73" s="16"/>
       <c r="I73" s="16"/>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="15">
@@ -10124,7 +10218,7 @@
       <c r="H74" s="16"/>
       <c r="I74" s="16"/>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="75" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="15">
@@ -10143,7 +10237,7 @@
       <c r="H75" s="16"/>
       <c r="I75" s="16"/>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="76" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="15">
@@ -10162,7 +10256,7 @@
       <c r="H76" s="16"/>
       <c r="I76" s="16"/>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="77" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="15">
@@ -10181,7 +10275,7 @@
       <c r="H77" s="16"/>
       <c r="I77" s="16"/>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="78" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="15">
@@ -10200,7 +10294,7 @@
       <c r="H78" s="16"/>
       <c r="I78" s="16"/>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="79" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="15">
@@ -10219,7 +10313,7 @@
       <c r="H79" s="16"/>
       <c r="I79" s="16"/>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="80" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="15">
@@ -10238,7 +10332,7 @@
       <c r="H80" s="16"/>
       <c r="I80" s="16"/>
     </row>
-    <row r="81" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="81" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="15">
@@ -10257,7 +10351,7 @@
       <c r="H81" s="16"/>
       <c r="I81" s="16"/>
     </row>
-    <row r="82" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="82" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="15">
@@ -10276,7 +10370,7 @@
       <c r="H82" s="16"/>
       <c r="I82" s="16"/>
     </row>
-    <row r="83" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="83" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="15">
@@ -10295,7 +10389,7 @@
       <c r="H83" s="16"/>
       <c r="I83" s="16"/>
     </row>
-    <row r="84" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="84" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="15">
@@ -10314,7 +10408,7 @@
       <c r="H84" s="16"/>
       <c r="I84" s="16"/>
     </row>
-    <row r="85" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="85" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="15">
@@ -10333,7 +10427,7 @@
       <c r="H85" s="16"/>
       <c r="I85" s="16"/>
     </row>
-    <row r="86" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="86" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="15">
@@ -10352,7 +10446,7 @@
       <c r="H86" s="16"/>
       <c r="I86" s="16"/>
     </row>
-    <row r="87" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="87" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="15">
@@ -10371,7 +10465,7 @@
       <c r="H87" s="16"/>
       <c r="I87" s="16"/>
     </row>
-    <row r="88" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="88" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="15">
@@ -10390,7 +10484,7 @@
       <c r="H88" s="16"/>
       <c r="I88" s="16"/>
     </row>
-    <row r="89" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="89" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="15">
@@ -10409,7 +10503,7 @@
       <c r="H89" s="16"/>
       <c r="I89" s="16"/>
     </row>
-    <row r="90" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="90" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="15">
@@ -10428,7 +10522,7 @@
       <c r="H90" s="16"/>
       <c r="I90" s="16"/>
     </row>
-    <row r="91" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="91" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="15">
@@ -10447,7 +10541,7 @@
       <c r="H91" s="16"/>
       <c r="I91" s="16"/>
     </row>
-    <row r="92" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="15">
@@ -10466,7 +10560,7 @@
       <c r="H92" s="16"/>
       <c r="I92" s="16"/>
     </row>
-    <row r="93" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="93" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="15">
@@ -10485,7 +10579,7 @@
       <c r="H93" s="16"/>
       <c r="I93" s="16"/>
     </row>
-    <row r="94" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="94" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="15">
@@ -10504,7 +10598,7 @@
       <c r="H94" s="16"/>
       <c r="I94" s="16"/>
     </row>
-    <row r="95" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="95" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="15">
@@ -10523,7 +10617,7 @@
       <c r="H95" s="16"/>
       <c r="I95" s="16"/>
     </row>
-    <row r="96" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="96" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="15">
@@ -10542,7 +10636,7 @@
       <c r="H96" s="16"/>
       <c r="I96" s="16"/>
     </row>
-    <row r="97" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="97" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="15">
@@ -10561,7 +10655,7 @@
       <c r="H97" s="16"/>
       <c r="I97" s="16"/>
     </row>
-    <row r="98" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="98" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="15">
@@ -10576,7 +10670,7 @@
       <c r="H98" s="16"/>
       <c r="I98" s="16"/>
     </row>
-    <row r="99" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="99" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="15">
@@ -10591,7 +10685,7 @@
       <c r="H99" s="16"/>
       <c r="I99" s="16"/>
     </row>
-    <row r="100" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="100" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="15">
@@ -10606,7 +10700,7 @@
       <c r="H100" s="16"/>
       <c r="I100" s="16"/>
     </row>
-    <row r="101" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="101" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="15">
@@ -10621,7 +10715,7 @@
       <c r="H101" s="16"/>
       <c r="I101" s="16"/>
     </row>
-    <row r="102" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="102" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="15">
@@ -10636,7 +10730,7 @@
       <c r="H102" s="16"/>
       <c r="I102" s="16"/>
     </row>
-    <row r="103" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="103" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="15">
@@ -10651,7 +10745,7 @@
       <c r="H103" s="16"/>
       <c r="I103" s="16"/>
     </row>
-    <row r="104" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="104" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="16"/>
@@ -10662,7 +10756,7 @@
       <c r="H104" s="16"/>
       <c r="I104" s="16"/>
     </row>
-    <row r="105" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="105" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
@@ -10673,7 +10767,7 @@
       <c r="H105" s="16"/>
       <c r="I105" s="16"/>
     </row>
-    <row r="106" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="106" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="16"/>
@@ -10684,7 +10778,7 @@
       <c r="H106" s="16"/>
       <c r="I106" s="16"/>
     </row>
-    <row r="107" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="107" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="16"/>
@@ -10695,7 +10789,7 @@
       <c r="H107" s="16"/>
       <c r="I107" s="16"/>
     </row>
-    <row r="108" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="108" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A108" s="13"/>
       <c r="B108" s="18" t="s">
         <v>11</v>
@@ -10708,7 +10802,7 @@
       <c r="H108" s="16"/>
       <c r="I108" s="16"/>
     </row>
-    <row r="109" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="109" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="15">
@@ -10723,7 +10817,7 @@
       <c r="H109" s="16"/>
       <c r="I109" s="16"/>
     </row>
-    <row r="110" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="110" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="15">
@@ -10738,7 +10832,7 @@
       <c r="H110" s="16"/>
       <c r="I110" s="16"/>
     </row>
-    <row r="111" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="111" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="15">
@@ -10753,7 +10847,7 @@
       <c r="H111" s="16"/>
       <c r="I111" s="16"/>
     </row>
-    <row r="112" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="112" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="15">
@@ -10768,7 +10862,7 @@
       <c r="H112" s="16"/>
       <c r="I112" s="16"/>
     </row>
-    <row r="113" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="113" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="15">
@@ -10783,7 +10877,7 @@
       <c r="H113" s="16"/>
       <c r="I113" s="16"/>
     </row>
-    <row r="114" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="114" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="15">
@@ -10798,7 +10892,7 @@
       <c r="H114" s="16"/>
       <c r="I114" s="16"/>
     </row>
-    <row r="115" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="115" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="15">
@@ -10813,7 +10907,7 @@
       <c r="H115" s="16"/>
       <c r="I115" s="16"/>
     </row>
-    <row r="116" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="116" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="15">
@@ -10828,7 +10922,7 @@
       <c r="H116" s="16"/>
       <c r="I116" s="16"/>
     </row>
-    <row r="117" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="117" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="15">
@@ -10843,7 +10937,7 @@
       <c r="H117" s="16"/>
       <c r="I117" s="16"/>
     </row>
-    <row r="118" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="118" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="15">
@@ -10858,7 +10952,7 @@
       <c r="H118" s="16"/>
       <c r="I118" s="16"/>
     </row>
-    <row r="119" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="119" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="15">
@@ -10873,7 +10967,7 @@
       <c r="H119" s="16"/>
       <c r="I119" s="16"/>
     </row>
-    <row r="120" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="120" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="15">
@@ -10888,7 +10982,7 @@
       <c r="H120" s="16"/>
       <c r="I120" s="16"/>
     </row>
-    <row r="121" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="121" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="15">
@@ -10903,7 +10997,7 @@
       <c r="H121" s="16"/>
       <c r="I121" s="16"/>
     </row>
-    <row r="122" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="122" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="15">
@@ -10918,7 +11012,7 @@
       <c r="H122" s="16"/>
       <c r="I122" s="16"/>
     </row>
-    <row r="123" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="123" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="15">
@@ -10933,7 +11027,7 @@
       <c r="H123" s="16"/>
       <c r="I123" s="16"/>
     </row>
-    <row r="124" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="124" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="15">
@@ -10948,7 +11042,7 @@
       <c r="H124" s="16"/>
       <c r="I124" s="16"/>
     </row>
-    <row r="125" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="125" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="15">
@@ -10963,7 +11057,7 @@
       <c r="H125" s="16"/>
       <c r="I125" s="16"/>
     </row>
-    <row r="126" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="126" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="15">
@@ -10978,7 +11072,7 @@
       <c r="H126" s="16"/>
       <c r="I126" s="16"/>
     </row>
-    <row r="127" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="127" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="15">
@@ -10993,7 +11087,7 @@
       <c r="H127" s="16"/>
       <c r="I127" s="16"/>
     </row>
-    <row r="128" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="128" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="15">
@@ -11008,7 +11102,7 @@
       <c r="H128" s="16"/>
       <c r="I128" s="16"/>
     </row>
-    <row r="129" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="129" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="15">
@@ -11023,7 +11117,7 @@
       <c r="H129" s="16"/>
       <c r="I129" s="16"/>
     </row>
-    <row r="130" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="130" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="15">
@@ -11038,7 +11132,7 @@
       <c r="H130" s="16"/>
       <c r="I130" s="16"/>
     </row>
-    <row r="131" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="131" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="15">
@@ -11053,7 +11147,7 @@
       <c r="H131" s="16"/>
       <c r="I131" s="16"/>
     </row>
-    <row r="132" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="132" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="15">
@@ -11068,7 +11162,7 @@
       <c r="H132" s="16"/>
       <c r="I132" s="16"/>
     </row>
-    <row r="133" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="133" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="15">
@@ -11083,7 +11177,7 @@
       <c r="H133" s="16"/>
       <c r="I133" s="16"/>
     </row>
-    <row r="134" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="134" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="15">
@@ -11098,7 +11192,7 @@
       <c r="H134" s="16"/>
       <c r="I134" s="16"/>
     </row>
-    <row r="135" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="135" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="15">
@@ -11113,7 +11207,7 @@
       <c r="H135" s="16"/>
       <c r="I135" s="16"/>
     </row>
-    <row r="136" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="136" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="15">
@@ -11128,7 +11222,7 @@
       <c r="H136" s="16"/>
       <c r="I136" s="16"/>
     </row>
-    <row r="137" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="137" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="15">
@@ -11143,7 +11237,7 @@
       <c r="H137" s="16"/>
       <c r="I137" s="16"/>
     </row>
-    <row r="138" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="138" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="15">
@@ -11158,7 +11252,7 @@
       <c r="H138" s="16"/>
       <c r="I138" s="16"/>
     </row>
-    <row r="139" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="139" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="15">
@@ -11173,7 +11267,7 @@
       <c r="H139" s="16"/>
       <c r="I139" s="16"/>
     </row>
-    <row r="140" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="140" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="15">
@@ -11188,7 +11282,7 @@
       <c r="H140" s="16"/>
       <c r="I140" s="16"/>
     </row>
-    <row r="141" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="141" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="15">
@@ -11203,7 +11297,7 @@
       <c r="H141" s="16"/>
       <c r="I141" s="16"/>
     </row>
-    <row r="142" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="142" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="15">
@@ -11218,7 +11312,7 @@
       <c r="H142" s="16"/>
       <c r="I142" s="16"/>
     </row>
-    <row r="143" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="143" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="15">
@@ -11233,7 +11327,7 @@
       <c r="H143" s="16"/>
       <c r="I143" s="16"/>
     </row>
-    <row r="144" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="144" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="15">
@@ -11248,7 +11342,7 @@
       <c r="H144" s="16"/>
       <c r="I144" s="16"/>
     </row>
-    <row r="145" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="145" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="15">
@@ -11263,7 +11357,7 @@
       <c r="H145" s="16"/>
       <c r="I145" s="16"/>
     </row>
-    <row r="146" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="146" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="15">
@@ -11278,7 +11372,7 @@
       <c r="H146" s="16"/>
       <c r="I146" s="16"/>
     </row>
-    <row r="147" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="147" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="15">
@@ -11293,7 +11387,7 @@
       <c r="H147" s="16"/>
       <c r="I147" s="16"/>
     </row>
-    <row r="148" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="148" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="15">
@@ -11308,7 +11402,7 @@
       <c r="H148" s="16"/>
       <c r="I148" s="16"/>
     </row>
-    <row r="149" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="149" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="15">
@@ -11323,7 +11417,7 @@
       <c r="H149" s="16"/>
       <c r="I149" s="16"/>
     </row>
-    <row r="150" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="150" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="15">
@@ -11338,7 +11432,7 @@
       <c r="H150" s="16"/>
       <c r="I150" s="16"/>
     </row>
-    <row r="151" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="151" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="15">
@@ -11353,7 +11447,7 @@
       <c r="H151" s="16"/>
       <c r="I151" s="16"/>
     </row>
-    <row r="152" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="152" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="15">
@@ -11368,7 +11462,7 @@
       <c r="H152" s="16"/>
       <c r="I152" s="16"/>
     </row>
-    <row r="153" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="153" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="15">
@@ -11383,7 +11477,7 @@
       <c r="H153" s="16"/>
       <c r="I153" s="16"/>
     </row>
-    <row r="154" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="154" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="15">
@@ -11398,7 +11492,7 @@
       <c r="H154" s="16"/>
       <c r="I154" s="16"/>
     </row>
-    <row r="155" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="155" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="15">
@@ -11413,7 +11507,7 @@
       <c r="H155" s="16"/>
       <c r="I155" s="16"/>
     </row>
-    <row r="156" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="156" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="15">
@@ -11428,7 +11522,7 @@
       <c r="H156" s="16"/>
       <c r="I156" s="16"/>
     </row>
-    <row r="157" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="157" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="15">
@@ -11443,7 +11537,7 @@
       <c r="H157" s="16"/>
       <c r="I157" s="16"/>
     </row>
-    <row r="158" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="158" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="15">
@@ -11458,7 +11552,7 @@
       <c r="H158" s="16"/>
       <c r="I158" s="16"/>
     </row>
-    <row r="159" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="159" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="15">
@@ -11473,7 +11567,7 @@
       <c r="H159" s="16"/>
       <c r="I159" s="16"/>
     </row>
-    <row r="160" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="160" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="15">
@@ -11488,7 +11582,7 @@
       <c r="H160" s="16"/>
       <c r="I160" s="16"/>
     </row>
-    <row r="161" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="161" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="15">
@@ -11503,7 +11597,7 @@
       <c r="H161" s="16"/>
       <c r="I161" s="16"/>
     </row>
-    <row r="162" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="162" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="15">
@@ -11518,7 +11612,7 @@
       <c r="H162" s="16"/>
       <c r="I162" s="16"/>
     </row>
-    <row r="163" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="163" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="15">
@@ -11533,7 +11627,7 @@
       <c r="H163" s="16"/>
       <c r="I163" s="16"/>
     </row>
-    <row r="164" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="164" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="15">
@@ -11548,7 +11642,7 @@
       <c r="H164" s="16"/>
       <c r="I164" s="16"/>
     </row>
-    <row r="165" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="165" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="15">
@@ -11563,7 +11657,7 @@
       <c r="H165" s="16"/>
       <c r="I165" s="16"/>
     </row>
-    <row r="166" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="166" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="15">
@@ -11578,7 +11672,7 @@
       <c r="H166" s="16"/>
       <c r="I166" s="16"/>
     </row>
-    <row r="167" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="167" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="15">
@@ -11593,7 +11687,7 @@
       <c r="H167" s="16"/>
       <c r="I167" s="16"/>
     </row>
-    <row r="168" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="168" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="15">
@@ -11608,7 +11702,7 @@
       <c r="H168" s="16"/>
       <c r="I168" s="16"/>
     </row>
-    <row r="169" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="169" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="15">
@@ -11623,7 +11717,7 @@
       <c r="H169" s="16"/>
       <c r="I169" s="16"/>
     </row>
-    <row r="170" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="170" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="15">
@@ -11638,7 +11732,7 @@
       <c r="H170" s="16"/>
       <c r="I170" s="16"/>
     </row>
-    <row r="171" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="171" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="15">
@@ -11653,7 +11747,7 @@
       <c r="H171" s="16"/>
       <c r="I171" s="16"/>
     </row>
-    <row r="172" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="172" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="15">
@@ -11668,7 +11762,7 @@
       <c r="H172" s="16"/>
       <c r="I172" s="16"/>
     </row>
-    <row r="173" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="173" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="15">
@@ -11683,7 +11777,7 @@
       <c r="H173" s="16"/>
       <c r="I173" s="16"/>
     </row>
-    <row r="174" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="174" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="15">
@@ -11698,7 +11792,7 @@
       <c r="H174" s="16"/>
       <c r="I174" s="16"/>
     </row>
-    <row r="175" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="175" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="15">
@@ -11713,7 +11807,7 @@
       <c r="H175" s="16"/>
       <c r="I175" s="16"/>
     </row>
-    <row r="176" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="176" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="15">
@@ -11728,7 +11822,7 @@
       <c r="H176" s="16"/>
       <c r="I176" s="16"/>
     </row>
-    <row r="177" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="177" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="15">
@@ -11743,7 +11837,7 @@
       <c r="H177" s="16"/>
       <c r="I177" s="16"/>
     </row>
-    <row r="178" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="178" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="15">
@@ -11758,7 +11852,7 @@
       <c r="H178" s="16"/>
       <c r="I178" s="16"/>
     </row>
-    <row r="179" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="179" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="15">
@@ -11773,7 +11867,7 @@
       <c r="H179" s="16"/>
       <c r="I179" s="16"/>
     </row>
-    <row r="180" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="180" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="15">
@@ -11788,7 +11882,7 @@
       <c r="H180" s="16"/>
       <c r="I180" s="16"/>
     </row>
-    <row r="181" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="181" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="15">
@@ -11803,7 +11897,7 @@
       <c r="H181" s="16"/>
       <c r="I181" s="16"/>
     </row>
-    <row r="182" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="182" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="15">
@@ -11818,7 +11912,7 @@
       <c r="H182" s="16"/>
       <c r="I182" s="16"/>
     </row>
-    <row r="183" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="183" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="15">
@@ -11833,7 +11927,7 @@
       <c r="H183" s="16"/>
       <c r="I183" s="16"/>
     </row>
-    <row r="184" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="184" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="15">
@@ -11848,7 +11942,7 @@
       <c r="H184" s="16"/>
       <c r="I184" s="16"/>
     </row>
-    <row r="185" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="185" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="15">
@@ -11863,7 +11957,7 @@
       <c r="H185" s="16"/>
       <c r="I185" s="16"/>
     </row>
-    <row r="186" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="186" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="15">
@@ -11878,7 +11972,7 @@
       <c r="H186" s="16"/>
       <c r="I186" s="16"/>
     </row>
-    <row r="187" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="187" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="15">
@@ -11893,7 +11987,7 @@
       <c r="H187" s="16"/>
       <c r="I187" s="16"/>
     </row>
-    <row r="188" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="188" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="15">
@@ -11908,7 +12002,7 @@
       <c r="H188" s="16"/>
       <c r="I188" s="16"/>
     </row>
-    <row r="189" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="189" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="15">
@@ -11923,7 +12017,7 @@
       <c r="H189" s="16"/>
       <c r="I189" s="16"/>
     </row>
-    <row r="190" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="190" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="15">
@@ -11938,7 +12032,7 @@
       <c r="H190" s="16"/>
       <c r="I190" s="16"/>
     </row>
-    <row r="191" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="191" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="15">
@@ -11953,7 +12047,7 @@
       <c r="H191" s="16"/>
       <c r="I191" s="16"/>
     </row>
-    <row r="192" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="192" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="15">
@@ -11968,7 +12062,7 @@
       <c r="H192" s="16"/>
       <c r="I192" s="16"/>
     </row>
-    <row r="193" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="193" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="15">
@@ -11983,7 +12077,7 @@
       <c r="H193" s="16"/>
       <c r="I193" s="16"/>
     </row>
-    <row r="194" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="194" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="15">
@@ -11998,7 +12092,7 @@
       <c r="H194" s="16"/>
       <c r="I194" s="16"/>
     </row>
-    <row r="195" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="195" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="15">
@@ -12013,7 +12107,7 @@
       <c r="H195" s="16"/>
       <c r="I195" s="16"/>
     </row>
-    <row r="196" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="196" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="15">
@@ -12028,7 +12122,7 @@
       <c r="H196" s="16"/>
       <c r="I196" s="16"/>
     </row>
-    <row r="197" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="197" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="15">
@@ -12043,7 +12137,7 @@
       <c r="H197" s="16"/>
       <c r="I197" s="16"/>
     </row>
-    <row r="198" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="198" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="15">
@@ -12058,7 +12152,7 @@
       <c r="H198" s="16"/>
       <c r="I198" s="16"/>
     </row>
-    <row r="199" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="199" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="15">
@@ -12073,7 +12167,7 @@
       <c r="H199" s="16"/>
       <c r="I199" s="16"/>
     </row>
-    <row r="200" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="200" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="15">
@@ -12088,7 +12182,7 @@
       <c r="H200" s="16"/>
       <c r="I200" s="16"/>
     </row>
-    <row r="201" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="201" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="15">
@@ -12103,7 +12197,7 @@
       <c r="H201" s="16"/>
       <c r="I201" s="16"/>
     </row>
-    <row r="202" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="202" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="15">
@@ -12118,7 +12212,7 @@
       <c r="H202" s="16"/>
       <c r="I202" s="16"/>
     </row>
-    <row r="203" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="203" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="15">
@@ -12133,7 +12227,7 @@
       <c r="H203" s="16"/>
       <c r="I203" s="16"/>
     </row>
-    <row r="204" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="204" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="16"/>
@@ -12144,7 +12238,7 @@
       <c r="H204" s="16"/>
       <c r="I204" s="16"/>
     </row>
-    <row r="205" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="205" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="16"/>
@@ -12155,7 +12249,7 @@
       <c r="H205" s="16"/>
       <c r="I205" s="16"/>
     </row>
-    <row r="206" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="206" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="16"/>
@@ -12166,7 +12260,7 @@
       <c r="H206" s="16"/>
       <c r="I206" s="16"/>
     </row>
-    <row r="207" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="207" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="16"/>
@@ -12177,7 +12271,7 @@
       <c r="H207" s="16"/>
       <c r="I207" s="16"/>
     </row>
-    <row r="208" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="208" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="16"/>
@@ -12188,7 +12282,7 @@
       <c r="H208" s="16"/>
       <c r="I208" s="16"/>
     </row>
-    <row r="209" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="209" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="16"/>
@@ -12199,7 +12293,7 @@
       <c r="H209" s="16"/>
       <c r="I209" s="16"/>
     </row>
-    <row r="210" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="210" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="16"/>
@@ -12210,7 +12304,7 @@
       <c r="H210" s="16"/>
       <c r="I210" s="16"/>
     </row>
-    <row r="211" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="211" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="16"/>
@@ -12221,7 +12315,7 @@
       <c r="H211" s="16"/>
       <c r="I211" s="16"/>
     </row>
-    <row r="212" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="212" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="16"/>
@@ -12232,7 +12326,7 @@
       <c r="H212" s="16"/>
       <c r="I212" s="16"/>
     </row>
-    <row r="213" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="213" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="16"/>
@@ -12243,7 +12337,7 @@
       <c r="H213" s="16"/>
       <c r="I213" s="16"/>
     </row>
-    <row r="214" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="214" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="16"/>
@@ -12254,7 +12348,7 @@
       <c r="H214" s="16"/>
       <c r="I214" s="16"/>
     </row>
-    <row r="215" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="215" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="16"/>
@@ -12265,7 +12359,7 @@
       <c r="H215" s="16"/>
       <c r="I215" s="16"/>
     </row>
-    <row r="216" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="216" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="16"/>
@@ -12276,7 +12370,7 @@
       <c r="H216" s="16"/>
       <c r="I216" s="16"/>
     </row>
-    <row r="217" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="217" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="16"/>
@@ -12287,7 +12381,7 @@
       <c r="H217" s="16"/>
       <c r="I217" s="16"/>
     </row>
-    <row r="218" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="218" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="16"/>
@@ -12298,7 +12392,7 @@
       <c r="H218" s="16"/>
       <c r="I218" s="16"/>
     </row>
-    <row r="219" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="219" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="16"/>
@@ -12309,7 +12403,7 @@
       <c r="H219" s="16"/>
       <c r="I219" s="16"/>
     </row>
-    <row r="220" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="220" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="16"/>
@@ -12320,7 +12414,7 @@
       <c r="H220" s="16"/>
       <c r="I220" s="16"/>
     </row>
-    <row r="221" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="221" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="16"/>
@@ -12331,7 +12425,7 @@
       <c r="H221" s="16"/>
       <c r="I221" s="16"/>
     </row>
-    <row r="222" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="222" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="16"/>
@@ -12342,7 +12436,7 @@
       <c r="H222" s="16"/>
       <c r="I222" s="16"/>
     </row>
-    <row r="223" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="223" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="16"/>
@@ -12353,7 +12447,7 @@
       <c r="H223" s="16"/>
       <c r="I223" s="16"/>
     </row>
-    <row r="224" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="224" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="16"/>
@@ -12364,7 +12458,7 @@
       <c r="H224" s="16"/>
       <c r="I224" s="16"/>
     </row>
-    <row r="225" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="225" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="16"/>
@@ -12375,7 +12469,7 @@
       <c r="H225" s="16"/>
       <c r="I225" s="16"/>
     </row>
-    <row r="226" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="226" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="16"/>
@@ -12386,7 +12480,7 @@
       <c r="H226" s="16"/>
       <c r="I226" s="16"/>
     </row>
-    <row r="227" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="227" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="16"/>
@@ -12397,7 +12491,7 @@
       <c r="H227" s="16"/>
       <c r="I227" s="16"/>
     </row>
-    <row r="228" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="228" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="16"/>
@@ -12408,7 +12502,7 @@
       <c r="H228" s="16"/>
       <c r="I228" s="16"/>
     </row>
-    <row r="229" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="229" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="16"/>
@@ -12419,7 +12513,7 @@
       <c r="H229" s="16"/>
       <c r="I229" s="16"/>
     </row>
-    <row r="230" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="230" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="16"/>
@@ -12430,7 +12524,7 @@
       <c r="H230" s="16"/>
       <c r="I230" s="16"/>
     </row>
-    <row r="231" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="231" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="16"/>
@@ -12441,7 +12535,7 @@
       <c r="H231" s="16"/>
       <c r="I231" s="16"/>
     </row>
-    <row r="232" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="232" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="16"/>
@@ -12452,7 +12546,7 @@
       <c r="H232" s="16"/>
       <c r="I232" s="16"/>
     </row>
-    <row r="233" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="233" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="16"/>
@@ -12463,7 +12557,7 @@
       <c r="H233" s="16"/>
       <c r="I233" s="16"/>
     </row>
-    <row r="234" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="234" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="16"/>
@@ -12474,7 +12568,7 @@
       <c r="H234" s="16"/>
       <c r="I234" s="16"/>
     </row>
-    <row r="235" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="235" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="16"/>
@@ -12485,7 +12579,7 @@
       <c r="H235" s="16"/>
       <c r="I235" s="16"/>
     </row>
-    <row r="236" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="236" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="16"/>
@@ -12496,7 +12590,7 @@
       <c r="H236" s="16"/>
       <c r="I236" s="16"/>
     </row>
-    <row r="237" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="237" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="16"/>
@@ -12507,7 +12601,7 @@
       <c r="H237" s="16"/>
       <c r="I237" s="16"/>
     </row>
-    <row r="238" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="238" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="16"/>
@@ -12518,7 +12612,7 @@
       <c r="H238" s="16"/>
       <c r="I238" s="16"/>
     </row>
-    <row r="239" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="239" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="16"/>
@@ -12529,7 +12623,7 @@
       <c r="H239" s="16"/>
       <c r="I239" s="16"/>
     </row>
-    <row r="240" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="240" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="16"/>
@@ -12540,7 +12634,7 @@
       <c r="H240" s="16"/>
       <c r="I240" s="16"/>
     </row>
-    <row r="241" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="241" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="16"/>
@@ -12551,7 +12645,7 @@
       <c r="H241" s="16"/>
       <c r="I241" s="16"/>
     </row>
-    <row r="242" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="242" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="16"/>
@@ -12562,7 +12656,7 @@
       <c r="H242" s="16"/>
       <c r="I242" s="16"/>
     </row>
-    <row r="243" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="243" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="16"/>
@@ -12573,7 +12667,7 @@
       <c r="H243" s="16"/>
       <c r="I243" s="16"/>
     </row>
-    <row r="244" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="244" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="16"/>
@@ -12584,7 +12678,7 @@
       <c r="H244" s="16"/>
       <c r="I244" s="16"/>
     </row>
-    <row r="245" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="245" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="16"/>
@@ -12595,7 +12689,7 @@
       <c r="H245" s="16"/>
       <c r="I245" s="16"/>
     </row>
-    <row r="246" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="246" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="16"/>
@@ -12606,7 +12700,7 @@
       <c r="H246" s="16"/>
       <c r="I246" s="16"/>
     </row>
-    <row r="247" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="247" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="16"/>
@@ -12617,7 +12711,7 @@
       <c r="H247" s="16"/>
       <c r="I247" s="16"/>
     </row>
-    <row r="248" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="248" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="16"/>
@@ -12628,7 +12722,7 @@
       <c r="H248" s="16"/>
       <c r="I248" s="16"/>
     </row>
-    <row r="249" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="249" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="16"/>
@@ -12639,7 +12733,7 @@
       <c r="H249" s="16"/>
       <c r="I249" s="16"/>
     </row>
-    <row r="250" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="250" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="16"/>
@@ -12650,7 +12744,7 @@
       <c r="H250" s="16"/>
       <c r="I250" s="16"/>
     </row>
-    <row r="251" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="251" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="16"/>
@@ -12661,7 +12755,7 @@
       <c r="H251" s="16"/>
       <c r="I251" s="16"/>
     </row>
-    <row r="252" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="252" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="16"/>
@@ -12672,7 +12766,7 @@
       <c r="H252" s="16"/>
       <c r="I252" s="16"/>
     </row>
-    <row r="253" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="253" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="16"/>
@@ -12683,7 +12777,7 @@
       <c r="H253" s="16"/>
       <c r="I253" s="16"/>
     </row>
-    <row r="254" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="254" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="16"/>
@@ -12694,7 +12788,7 @@
       <c r="H254" s="16"/>
       <c r="I254" s="16"/>
     </row>
-    <row r="255" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="255" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="16"/>
@@ -12705,7 +12799,7 @@
       <c r="H255" s="16"/>
       <c r="I255" s="16"/>
     </row>
-    <row r="256" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="256" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="16"/>
@@ -12716,7 +12810,7 @@
       <c r="H256" s="16"/>
       <c r="I256" s="16"/>
     </row>
-    <row r="257" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="257" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="16"/>
@@ -12727,7 +12821,7 @@
       <c r="H257" s="16"/>
       <c r="I257" s="16"/>
     </row>
-    <row r="258" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="258" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="16"/>
@@ -12738,7 +12832,7 @@
       <c r="H258" s="16"/>
       <c r="I258" s="16"/>
     </row>
-    <row r="259" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="259" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="16"/>
@@ -12749,7 +12843,7 @@
       <c r="H259" s="16"/>
       <c r="I259" s="16"/>
     </row>
-    <row r="260" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="260" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="16"/>
@@ -12760,7 +12854,7 @@
       <c r="H260" s="16"/>
       <c r="I260" s="16"/>
     </row>
-    <row r="261" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="261" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="16"/>
@@ -12771,7 +12865,7 @@
       <c r="H261" s="16"/>
       <c r="I261" s="16"/>
     </row>
-    <row r="262" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="262" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="16"/>
@@ -12782,7 +12876,7 @@
       <c r="H262" s="16"/>
       <c r="I262" s="16"/>
     </row>
-    <row r="263" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="263" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="16"/>
@@ -12809,10 +12903,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G263"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="19.899999999999999" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
-    <col min="1" max="8" width="16.28515625" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="16.28515625" style="19"/>
+    <col min="1" max="8" width="16.26953125" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="16.26953125" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
@@ -12863,7 +12957,7 @@
         <v>6.6419999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="15">
@@ -12883,7 +12977,7 @@
         <v>6.6429999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="15">
@@ -12903,7 +12997,7 @@
         <v>6.6449999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="13"/>
       <c r="B6" s="14"/>
       <c r="C6" s="15">
@@ -12923,7 +13017,7 @@
         <v>6.6479999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="13"/>
       <c r="B7" s="14"/>
       <c r="C7" s="15">
@@ -12943,7 +13037,7 @@
         <v>6.6509999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="15">
@@ -12963,7 +13057,7 @@
         <v>6.657</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="15">
@@ -12983,7 +13077,7 @@
         <v>6.6609999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="14"/>
       <c r="C10" s="15">
@@ -13003,7 +13097,7 @@
         <v>6.6690000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="15">
@@ -13023,7 +13117,7 @@
         <v>6.6929999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="15">
@@ -13043,7 +13137,7 @@
         <v>7.024</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="15">
@@ -13063,7 +13157,7 @@
         <v>7.1239999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="15">
@@ -13083,7 +13177,7 @@
         <v>7.1769999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="15">
@@ -13103,7 +13197,7 @@
         <v>7.234</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="15">
@@ -13123,7 +13217,7 @@
         <v>7.2729999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="15">
@@ -13143,7 +13237,7 @@
         <v>7.331999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="15">
@@ -13163,7 +13257,7 @@
         <v>7.363999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="15">
@@ -13183,7 +13277,7 @@
         <v>7.4030000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="15">
@@ -13203,7 +13297,7 @@
         <v>7.4339999999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="15">
@@ -13223,7 +13317,7 @@
         <v>7.4870000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="15">
@@ -13243,7 +13337,7 @@
         <v>7.5540000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="15">
@@ -13263,7 +13357,7 @@
         <v>7.6379999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="15">
@@ -13283,7 +13377,7 @@
         <v>7.8569999999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="15">
@@ -13303,7 +13397,7 @@
         <v>7.9990000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="15">
@@ -13323,7 +13417,7 @@
         <v>8.4169999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="15">
@@ -13343,7 +13437,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15">
@@ -13363,7 +13457,7 @@
         <v>10.090999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="15">
@@ -13383,7 +13477,7 @@
         <v>10.462</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="15">
@@ -13403,7 +13497,7 @@
         <v>10.802</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="15">
@@ -13423,7 +13517,7 @@
         <v>10.968</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="15">
@@ -13443,7 +13537,7 @@
         <v>11.154999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="15">
@@ -13463,7 +13557,7 @@
         <v>11.266999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="15">
@@ -13483,7 +13577,7 @@
         <v>11.365</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="35" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="15">
@@ -13503,7 +13597,7 @@
         <v>11.444000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="15">
@@ -13523,7 +13617,7 @@
         <v>11.554</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="15">
@@ -13543,7 +13637,7 @@
         <v>11.647</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="15">
@@ -13563,7 +13657,7 @@
         <v>11.779</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="15">
@@ -13583,7 +13677,7 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="15">
@@ -13603,7 +13697,7 @@
         <v>11.92</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="41" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="15">
@@ -13623,7 +13717,7 @@
         <v>12.025</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="42" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="15">
@@ -13643,7 +13737,7 @@
         <v>12.107000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="15">
@@ -13663,7 +13757,7 @@
         <v>12.233000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="44" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="15">
@@ -13683,7 +13777,7 @@
         <v>12.358000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="45" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="15">
@@ -13703,7 +13797,7 @@
         <v>12.407</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="46" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="15">
@@ -13723,7 +13817,7 @@
         <v>12.509</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="47" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="15">
@@ -13743,7 +13837,7 @@
         <v>12.606</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="48" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="15">
@@ -13763,7 +13857,7 @@
         <v>12.686</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="49" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="15">
@@ -13783,7 +13877,7 @@
         <v>12.747</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="50" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="15">
@@ -13803,7 +13897,7 @@
         <v>12.811</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="51" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="15">
@@ -13823,7 +13917,7 @@
         <v>12.871</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="15">
@@ -13843,7 +13937,7 @@
         <v>12.932</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="53" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="15">
@@ -13863,7 +13957,7 @@
         <v>12.983000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="54" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="15">
@@ -13883,7 +13977,7 @@
         <v>13.042</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="55" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="15">
@@ -13903,7 +13997,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="56" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="15">
@@ -13923,7 +14017,7 @@
         <v>13.185</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="15">
@@ -13943,7 +14037,7 @@
         <v>13.255000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="58" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="15">
@@ -13963,7 +14057,7 @@
         <v>13.308</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="59" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="15">
@@ -13983,7 +14077,7 @@
         <v>13.34</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="15">
@@ -14003,7 +14097,7 @@
         <v>13.397</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="15">
@@ -14023,7 +14117,7 @@
         <v>13.438000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="62" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="15">
@@ -14043,7 +14137,7 @@
         <v>13.477</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="15">
@@ -14063,7 +14157,7 @@
         <v>13.519</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="64" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="15">
@@ -14083,7 +14177,7 @@
         <v>13.557</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="65" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="15">
@@ -14103,7 +14197,7 @@
         <v>13.624000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="66" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="15">
@@ -14123,7 +14217,7 @@
         <v>13.73</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="15">
@@ -14143,7 +14237,7 @@
         <v>13.897</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="15">
@@ -14163,7 +14257,7 @@
         <v>13.996</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="69" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="15">
@@ -14183,7 +14277,7 @@
         <v>14.053000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="70" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="15">
@@ -14203,7 +14297,7 @@
         <v>14.151</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="71" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="15">
@@ -14223,7 +14317,7 @@
         <v>14.200000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="72" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="15">
@@ -14243,7 +14337,7 @@
         <v>14.234</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="73" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="15">
@@ -14263,7 +14357,7 @@
         <v>14.273</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="15">
@@ -14283,7 +14377,7 @@
         <v>14.298</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="75" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="15">
@@ -14303,7 +14397,7 @@
         <v>14.325000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="76" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="15">
@@ -14323,7 +14417,7 @@
         <v>14.351000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="77" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="15">
@@ -14343,7 +14437,7 @@
         <v>14.370000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="78" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="15">
@@ -14363,7 +14457,7 @@
         <v>14.387</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="79" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="15">
@@ -14383,7 +14477,7 @@
         <v>14.397</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="80" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="15">
@@ -14403,7 +14497,7 @@
         <v>14.407999999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="81" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="15">
@@ -14423,7 +14517,7 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="82" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="15">
@@ -14443,7 +14537,7 @@
         <v>14.434000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="83" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="15">
@@ -14463,7 +14557,7 @@
         <v>14.441000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="84" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="15">
@@ -14483,7 +14577,7 @@
         <v>14.452</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="85" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="15">
@@ -14503,7 +14597,7 @@
         <v>14.461</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="86" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="15">
@@ -14523,7 +14617,7 @@
         <v>14.473000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="87" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="15">
@@ -14543,7 +14637,7 @@
         <v>14.477</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="88" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="15">
@@ -14563,7 +14657,7 @@
         <v>14.489000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="89" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="15">
@@ -14583,7 +14677,7 @@
         <v>14.498000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="90" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="15">
@@ -14603,7 +14697,7 @@
         <v>14.507</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="91" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="15">
@@ -14623,7 +14717,7 @@
         <v>14.516999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="15">
@@ -14643,7 +14737,7 @@
         <v>14.525</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="93" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="15">
@@ -14663,7 +14757,7 @@
         <v>14.531000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="94" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="15">
@@ -14683,7 +14777,7 @@
         <v>14.539</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="95" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="15">
@@ -14703,7 +14797,7 @@
         <v>14.544</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="96" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="15">
@@ -14723,7 +14817,7 @@
         <v>14.554</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="97" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="15">
@@ -14743,7 +14837,7 @@
         <v>14.561</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="98" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="15">
@@ -14759,7 +14853,7 @@
         <v>14.569000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="99" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="15">
@@ -14775,7 +14869,7 @@
         <v>14.576000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="100" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="15">
@@ -14791,7 +14885,7 @@
         <v>14.586</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="101" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="15">
@@ -14807,7 +14901,7 @@
         <v>14.593</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="102" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="15">
@@ -14823,7 +14917,7 @@
         <v>14.601000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="103" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="15">
@@ -14839,7 +14933,7 @@
         <v>14.609</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="104" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="16"/>
@@ -14848,7 +14942,7 @@
       <c r="F104" s="16"/>
       <c r="G104" s="16"/>
     </row>
-    <row r="105" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="105" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
@@ -14857,7 +14951,7 @@
       <c r="F105" s="16"/>
       <c r="G105" s="16"/>
     </row>
-    <row r="106" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="106" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="16"/>
@@ -14866,7 +14960,7 @@
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
     </row>
-    <row r="107" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="107" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="16"/>
@@ -14875,7 +14969,7 @@
       <c r="F107" s="16"/>
       <c r="G107" s="16"/>
     </row>
-    <row r="108" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="108" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A108" s="13"/>
       <c r="B108" s="18" t="s">
         <v>11</v>
@@ -14886,7 +14980,7 @@
       <c r="F108" s="16"/>
       <c r="G108" s="16"/>
     </row>
-    <row r="109" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="109" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="15">
@@ -14899,7 +14993,7 @@
       <c r="F109" s="16"/>
       <c r="G109" s="16"/>
     </row>
-    <row r="110" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="110" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="15">
@@ -14912,7 +15006,7 @@
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
     </row>
-    <row r="111" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="111" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="15">
@@ -14925,7 +15019,7 @@
       <c r="F111" s="16"/>
       <c r="G111" s="16"/>
     </row>
-    <row r="112" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="112" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="15">
@@ -14938,7 +15032,7 @@
       <c r="F112" s="16"/>
       <c r="G112" s="16"/>
     </row>
-    <row r="113" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="113" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="15">
@@ -14951,7 +15045,7 @@
       <c r="F113" s="16"/>
       <c r="G113" s="16"/>
     </row>
-    <row r="114" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="114" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="15">
@@ -14964,7 +15058,7 @@
       <c r="F114" s="16"/>
       <c r="G114" s="16"/>
     </row>
-    <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="115" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="15">
@@ -14977,7 +15071,7 @@
       <c r="F115" s="16"/>
       <c r="G115" s="16"/>
     </row>
-    <row r="116" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="116" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="15">
@@ -14990,7 +15084,7 @@
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
     </row>
-    <row r="117" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="117" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="15">
@@ -15003,7 +15097,7 @@
       <c r="F117" s="16"/>
       <c r="G117" s="16"/>
     </row>
-    <row r="118" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="118" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="15">
@@ -15016,7 +15110,7 @@
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
     </row>
-    <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="119" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="15">
@@ -15029,7 +15123,7 @@
       <c r="F119" s="16"/>
       <c r="G119" s="16"/>
     </row>
-    <row r="120" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="120" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="15">
@@ -15042,7 +15136,7 @@
       <c r="F120" s="16"/>
       <c r="G120" s="16"/>
     </row>
-    <row r="121" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="121" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="15">
@@ -15055,7 +15149,7 @@
       <c r="F121" s="16"/>
       <c r="G121" s="16"/>
     </row>
-    <row r="122" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="122" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="15">
@@ -15068,7 +15162,7 @@
       <c r="F122" s="16"/>
       <c r="G122" s="16"/>
     </row>
-    <row r="123" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="123" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="15">
@@ -15081,7 +15175,7 @@
       <c r="F123" s="16"/>
       <c r="G123" s="16"/>
     </row>
-    <row r="124" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="124" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="15">
@@ -15094,7 +15188,7 @@
       <c r="F124" s="16"/>
       <c r="G124" s="16"/>
     </row>
-    <row r="125" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="125" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="15">
@@ -15107,7 +15201,7 @@
       <c r="F125" s="16"/>
       <c r="G125" s="16"/>
     </row>
-    <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="126" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="15">
@@ -15120,7 +15214,7 @@
       <c r="F126" s="16"/>
       <c r="G126" s="16"/>
     </row>
-    <row r="127" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="127" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="15">
@@ -15133,7 +15227,7 @@
       <c r="F127" s="16"/>
       <c r="G127" s="16"/>
     </row>
-    <row r="128" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="128" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="15">
@@ -15146,7 +15240,7 @@
       <c r="F128" s="16"/>
       <c r="G128" s="16"/>
     </row>
-    <row r="129" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="129" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="15">
@@ -15159,7 +15253,7 @@
       <c r="F129" s="16"/>
       <c r="G129" s="16"/>
     </row>
-    <row r="130" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="130" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="15">
@@ -15172,7 +15266,7 @@
       <c r="F130" s="16"/>
       <c r="G130" s="16"/>
     </row>
-    <row r="131" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="131" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="15">
@@ -15185,7 +15279,7 @@
       <c r="F131" s="16"/>
       <c r="G131" s="16"/>
     </row>
-    <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="132" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="15">
@@ -15198,7 +15292,7 @@
       <c r="F132" s="16"/>
       <c r="G132" s="16"/>
     </row>
-    <row r="133" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="133" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="15">
@@ -15211,7 +15305,7 @@
       <c r="F133" s="16"/>
       <c r="G133" s="16"/>
     </row>
-    <row r="134" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="134" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="15">
@@ -15224,7 +15318,7 @@
       <c r="F134" s="16"/>
       <c r="G134" s="16"/>
     </row>
-    <row r="135" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="135" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="15">
@@ -15237,7 +15331,7 @@
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
     </row>
-    <row r="136" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="136" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="15">
@@ -15250,7 +15344,7 @@
       <c r="F136" s="16"/>
       <c r="G136" s="16"/>
     </row>
-    <row r="137" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="137" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="15">
@@ -15263,7 +15357,7 @@
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
     </row>
-    <row r="138" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="138" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="15">
@@ -15276,7 +15370,7 @@
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
     </row>
-    <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="139" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="15">
@@ -15289,7 +15383,7 @@
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
     </row>
-    <row r="140" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="140" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="15">
@@ -15302,7 +15396,7 @@
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
     </row>
-    <row r="141" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="141" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="15">
@@ -15315,7 +15409,7 @@
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
     </row>
-    <row r="142" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="142" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="15">
@@ -15328,7 +15422,7 @@
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
     </row>
-    <row r="143" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="143" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="15">
@@ -15341,7 +15435,7 @@
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
     </row>
-    <row r="144" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="144" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="15">
@@ -15354,7 +15448,7 @@
       <c r="F144" s="16"/>
       <c r="G144" s="16"/>
     </row>
-    <row r="145" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="145" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="15">
@@ -15367,7 +15461,7 @@
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
     </row>
-    <row r="146" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="146" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="15">
@@ -15380,7 +15474,7 @@
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
     </row>
-    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="147" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="15">
@@ -15393,7 +15487,7 @@
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
     </row>
-    <row r="148" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="148" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="15">
@@ -15406,7 +15500,7 @@
       <c r="F148" s="16"/>
       <c r="G148" s="16"/>
     </row>
-    <row r="149" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="149" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="15">
@@ -15419,7 +15513,7 @@
       <c r="F149" s="16"/>
       <c r="G149" s="16"/>
     </row>
-    <row r="150" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="150" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="15">
@@ -15432,7 +15526,7 @@
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
     </row>
-    <row r="151" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="151" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="15">
@@ -15445,7 +15539,7 @@
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
     </row>
-    <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="152" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="15">
@@ -15458,7 +15552,7 @@
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
     </row>
-    <row r="153" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="153" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="15">
@@ -15471,7 +15565,7 @@
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
     </row>
-    <row r="154" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="154" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="15">
@@ -15484,7 +15578,7 @@
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
     </row>
-    <row r="155" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="155" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="15">
@@ -15497,7 +15591,7 @@
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
     </row>
-    <row r="156" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="156" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="15">
@@ -15510,7 +15604,7 @@
       <c r="F156" s="16"/>
       <c r="G156" s="16"/>
     </row>
-    <row r="157" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="157" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="15">
@@ -15523,7 +15617,7 @@
       <c r="F157" s="16"/>
       <c r="G157" s="16"/>
     </row>
-    <row r="158" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="158" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="15">
@@ -15536,7 +15630,7 @@
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
     </row>
-    <row r="159" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="159" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="15">
@@ -15549,7 +15643,7 @@
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
     </row>
-    <row r="160" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="160" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="15">
@@ -15562,7 +15656,7 @@
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
     </row>
-    <row r="161" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="161" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="15">
@@ -15575,7 +15669,7 @@
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
     </row>
-    <row r="162" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="162" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="15">
@@ -15588,7 +15682,7 @@
       <c r="F162" s="16"/>
       <c r="G162" s="16"/>
     </row>
-    <row r="163" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="163" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="15">
@@ -15601,7 +15695,7 @@
       <c r="F163" s="16"/>
       <c r="G163" s="16"/>
     </row>
-    <row r="164" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="164" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="15">
@@ -15614,7 +15708,7 @@
       <c r="F164" s="16"/>
       <c r="G164" s="16"/>
     </row>
-    <row r="165" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="165" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="15">
@@ -15627,7 +15721,7 @@
       <c r="F165" s="16"/>
       <c r="G165" s="16"/>
     </row>
-    <row r="166" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="166" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="15">
@@ -15640,7 +15734,7 @@
       <c r="F166" s="16"/>
       <c r="G166" s="16"/>
     </row>
-    <row r="167" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="167" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="15">
@@ -15653,7 +15747,7 @@
       <c r="F167" s="16"/>
       <c r="G167" s="16"/>
     </row>
-    <row r="168" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="168" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="15">
@@ -15666,7 +15760,7 @@
       <c r="F168" s="16"/>
       <c r="G168" s="16"/>
     </row>
-    <row r="169" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="169" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="15">
@@ -15679,7 +15773,7 @@
       <c r="F169" s="16"/>
       <c r="G169" s="16"/>
     </row>
-    <row r="170" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="170" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="15">
@@ -15692,7 +15786,7 @@
       <c r="F170" s="16"/>
       <c r="G170" s="16"/>
     </row>
-    <row r="171" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="171" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="15">
@@ -15705,7 +15799,7 @@
       <c r="F171" s="16"/>
       <c r="G171" s="16"/>
     </row>
-    <row r="172" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="172" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="15">
@@ -15718,7 +15812,7 @@
       <c r="F172" s="16"/>
       <c r="G172" s="16"/>
     </row>
-    <row r="173" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="173" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="15">
@@ -15731,7 +15825,7 @@
       <c r="F173" s="16"/>
       <c r="G173" s="16"/>
     </row>
-    <row r="174" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="174" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="15">
@@ -15744,7 +15838,7 @@
       <c r="F174" s="16"/>
       <c r="G174" s="16"/>
     </row>
-    <row r="175" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="175" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="15">
@@ -15757,7 +15851,7 @@
       <c r="F175" s="16"/>
       <c r="G175" s="16"/>
     </row>
-    <row r="176" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="176" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="15">
@@ -15770,7 +15864,7 @@
       <c r="F176" s="16"/>
       <c r="G176" s="16"/>
     </row>
-    <row r="177" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="177" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="15">
@@ -15783,7 +15877,7 @@
       <c r="F177" s="16"/>
       <c r="G177" s="16"/>
     </row>
-    <row r="178" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="178" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="15">
@@ -15796,7 +15890,7 @@
       <c r="F178" s="16"/>
       <c r="G178" s="16"/>
     </row>
-    <row r="179" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="179" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="15">
@@ -15809,7 +15903,7 @@
       <c r="F179" s="16"/>
       <c r="G179" s="16"/>
     </row>
-    <row r="180" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="180" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="15">
@@ -15822,7 +15916,7 @@
       <c r="F180" s="16"/>
       <c r="G180" s="16"/>
     </row>
-    <row r="181" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="181" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="15">
@@ -15835,7 +15929,7 @@
       <c r="F181" s="16"/>
       <c r="G181" s="16"/>
     </row>
-    <row r="182" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="182" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="15">
@@ -15848,7 +15942,7 @@
       <c r="F182" s="16"/>
       <c r="G182" s="16"/>
     </row>
-    <row r="183" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="183" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="15">
@@ -15861,7 +15955,7 @@
       <c r="F183" s="16"/>
       <c r="G183" s="16"/>
     </row>
-    <row r="184" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="184" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="15">
@@ -15874,7 +15968,7 @@
       <c r="F184" s="16"/>
       <c r="G184" s="16"/>
     </row>
-    <row r="185" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="185" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="15">
@@ -15887,7 +15981,7 @@
       <c r="F185" s="16"/>
       <c r="G185" s="16"/>
     </row>
-    <row r="186" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="186" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="15">
@@ -15900,7 +15994,7 @@
       <c r="F186" s="16"/>
       <c r="G186" s="16"/>
     </row>
-    <row r="187" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="187" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="15">
@@ -15913,7 +16007,7 @@
       <c r="F187" s="16"/>
       <c r="G187" s="16"/>
     </row>
-    <row r="188" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="188" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="15">
@@ -15926,7 +16020,7 @@
       <c r="F188" s="16"/>
       <c r="G188" s="16"/>
     </row>
-    <row r="189" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="189" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="15">
@@ -15939,7 +16033,7 @@
       <c r="F189" s="16"/>
       <c r="G189" s="16"/>
     </row>
-    <row r="190" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="190" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="15">
@@ -15952,7 +16046,7 @@
       <c r="F190" s="16"/>
       <c r="G190" s="16"/>
     </row>
-    <row r="191" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="191" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="15">
@@ -15965,7 +16059,7 @@
       <c r="F191" s="16"/>
       <c r="G191" s="16"/>
     </row>
-    <row r="192" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="192" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="15">
@@ -15978,7 +16072,7 @@
       <c r="F192" s="16"/>
       <c r="G192" s="16"/>
     </row>
-    <row r="193" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="193" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="15">
@@ -15991,7 +16085,7 @@
       <c r="F193" s="16"/>
       <c r="G193" s="16"/>
     </row>
-    <row r="194" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="194" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="15">
@@ -16004,7 +16098,7 @@
       <c r="F194" s="16"/>
       <c r="G194" s="16"/>
     </row>
-    <row r="195" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="195" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="15">
@@ -16017,7 +16111,7 @@
       <c r="F195" s="16"/>
       <c r="G195" s="16"/>
     </row>
-    <row r="196" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="196" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="15">
@@ -16030,7 +16124,7 @@
       <c r="F196" s="16"/>
       <c r="G196" s="16"/>
     </row>
-    <row r="197" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="197" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="15">
@@ -16043,7 +16137,7 @@
       <c r="F197" s="16"/>
       <c r="G197" s="16"/>
     </row>
-    <row r="198" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="198" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="15">
@@ -16056,7 +16150,7 @@
       <c r="F198" s="16"/>
       <c r="G198" s="16"/>
     </row>
-    <row r="199" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="199" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="15">
@@ -16069,7 +16163,7 @@
       <c r="F199" s="16"/>
       <c r="G199" s="16"/>
     </row>
-    <row r="200" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="200" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="15">
@@ -16082,7 +16176,7 @@
       <c r="F200" s="16"/>
       <c r="G200" s="16"/>
     </row>
-    <row r="201" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="201" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="15">
@@ -16095,7 +16189,7 @@
       <c r="F201" s="16"/>
       <c r="G201" s="16"/>
     </row>
-    <row r="202" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="202" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="15">
@@ -16108,7 +16202,7 @@
       <c r="F202" s="16"/>
       <c r="G202" s="16"/>
     </row>
-    <row r="203" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="203" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="15">
@@ -16121,7 +16215,7 @@
       <c r="F203" s="16"/>
       <c r="G203" s="16"/>
     </row>
-    <row r="204" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="204" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="16"/>
@@ -16130,7 +16224,7 @@
       <c r="F204" s="16"/>
       <c r="G204" s="16"/>
     </row>
-    <row r="205" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="205" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="16"/>
@@ -16139,7 +16233,7 @@
       <c r="F205" s="16"/>
       <c r="G205" s="16"/>
     </row>
-    <row r="206" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="206" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="16"/>
@@ -16148,7 +16242,7 @@
       <c r="F206" s="16"/>
       <c r="G206" s="16"/>
     </row>
-    <row r="207" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="207" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="16"/>
@@ -16157,7 +16251,7 @@
       <c r="F207" s="16"/>
       <c r="G207" s="16"/>
     </row>
-    <row r="208" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="208" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="16"/>
@@ -16166,7 +16260,7 @@
       <c r="F208" s="16"/>
       <c r="G208" s="16"/>
     </row>
-    <row r="209" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="209" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="16"/>
@@ -16175,7 +16269,7 @@
       <c r="F209" s="16"/>
       <c r="G209" s="16"/>
     </row>
-    <row r="210" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="210" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="16"/>
@@ -16184,7 +16278,7 @@
       <c r="F210" s="16"/>
       <c r="G210" s="16"/>
     </row>
-    <row r="211" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="211" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="16"/>
@@ -16193,7 +16287,7 @@
       <c r="F211" s="16"/>
       <c r="G211" s="16"/>
     </row>
-    <row r="212" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="212" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="16"/>
@@ -16202,7 +16296,7 @@
       <c r="F212" s="16"/>
       <c r="G212" s="16"/>
     </row>
-    <row r="213" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="213" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="16"/>
@@ -16211,7 +16305,7 @@
       <c r="F213" s="16"/>
       <c r="G213" s="16"/>
     </row>
-    <row r="214" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="214" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="16"/>
@@ -16220,7 +16314,7 @@
       <c r="F214" s="16"/>
       <c r="G214" s="16"/>
     </row>
-    <row r="215" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="215" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="16"/>
@@ -16229,7 +16323,7 @@
       <c r="F215" s="16"/>
       <c r="G215" s="16"/>
     </row>
-    <row r="216" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="216" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="16"/>
@@ -16238,7 +16332,7 @@
       <c r="F216" s="16"/>
       <c r="G216" s="16"/>
     </row>
-    <row r="217" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="217" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="16"/>
@@ -16247,7 +16341,7 @@
       <c r="F217" s="16"/>
       <c r="G217" s="16"/>
     </row>
-    <row r="218" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="218" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="16"/>
@@ -16256,7 +16350,7 @@
       <c r="F218" s="16"/>
       <c r="G218" s="16"/>
     </row>
-    <row r="219" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="219" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="16"/>
@@ -16265,7 +16359,7 @@
       <c r="F219" s="16"/>
       <c r="G219" s="16"/>
     </row>
-    <row r="220" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="220" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="16"/>
@@ -16274,7 +16368,7 @@
       <c r="F220" s="16"/>
       <c r="G220" s="16"/>
     </row>
-    <row r="221" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="221" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="16"/>
@@ -16283,7 +16377,7 @@
       <c r="F221" s="16"/>
       <c r="G221" s="16"/>
     </row>
-    <row r="222" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="222" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="16"/>
@@ -16292,7 +16386,7 @@
       <c r="F222" s="16"/>
       <c r="G222" s="16"/>
     </row>
-    <row r="223" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="223" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="16"/>
@@ -16301,7 +16395,7 @@
       <c r="F223" s="16"/>
       <c r="G223" s="16"/>
     </row>
-    <row r="224" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="224" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="16"/>
@@ -16310,7 +16404,7 @@
       <c r="F224" s="16"/>
       <c r="G224" s="16"/>
     </row>
-    <row r="225" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="225" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="16"/>
@@ -16319,7 +16413,7 @@
       <c r="F225" s="16"/>
       <c r="G225" s="16"/>
     </row>
-    <row r="226" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="226" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="16"/>
@@ -16328,7 +16422,7 @@
       <c r="F226" s="16"/>
       <c r="G226" s="16"/>
     </row>
-    <row r="227" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="227" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="16"/>
@@ -16337,7 +16431,7 @@
       <c r="F227" s="16"/>
       <c r="G227" s="16"/>
     </row>
-    <row r="228" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="228" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="16"/>
@@ -16346,7 +16440,7 @@
       <c r="F228" s="16"/>
       <c r="G228" s="16"/>
     </row>
-    <row r="229" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="229" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="16"/>
@@ -16355,7 +16449,7 @@
       <c r="F229" s="16"/>
       <c r="G229" s="16"/>
     </row>
-    <row r="230" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="230" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="16"/>
@@ -16364,7 +16458,7 @@
       <c r="F230" s="16"/>
       <c r="G230" s="16"/>
     </row>
-    <row r="231" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="231" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="16"/>
@@ -16373,7 +16467,7 @@
       <c r="F231" s="16"/>
       <c r="G231" s="16"/>
     </row>
-    <row r="232" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="232" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="16"/>
@@ -16382,7 +16476,7 @@
       <c r="F232" s="16"/>
       <c r="G232" s="16"/>
     </row>
-    <row r="233" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="233" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="16"/>
@@ -16391,7 +16485,7 @@
       <c r="F233" s="16"/>
       <c r="G233" s="16"/>
     </row>
-    <row r="234" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="234" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="16"/>
@@ -16400,7 +16494,7 @@
       <c r="F234" s="16"/>
       <c r="G234" s="16"/>
     </row>
-    <row r="235" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="235" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="16"/>
@@ -16409,7 +16503,7 @@
       <c r="F235" s="16"/>
       <c r="G235" s="16"/>
     </row>
-    <row r="236" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="236" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="16"/>
@@ -16418,7 +16512,7 @@
       <c r="F236" s="16"/>
       <c r="G236" s="16"/>
     </row>
-    <row r="237" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="237" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="16"/>
@@ -16427,7 +16521,7 @@
       <c r="F237" s="16"/>
       <c r="G237" s="16"/>
     </row>
-    <row r="238" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="238" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="16"/>
@@ -16436,7 +16530,7 @@
       <c r="F238" s="16"/>
       <c r="G238" s="16"/>
     </row>
-    <row r="239" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="239" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="16"/>
@@ -16445,7 +16539,7 @@
       <c r="F239" s="16"/>
       <c r="G239" s="16"/>
     </row>
-    <row r="240" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="240" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="16"/>
@@ -16454,7 +16548,7 @@
       <c r="F240" s="16"/>
       <c r="G240" s="16"/>
     </row>
-    <row r="241" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="241" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="16"/>
@@ -16463,7 +16557,7 @@
       <c r="F241" s="16"/>
       <c r="G241" s="16"/>
     </row>
-    <row r="242" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="242" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="16"/>
@@ -16472,7 +16566,7 @@
       <c r="F242" s="16"/>
       <c r="G242" s="16"/>
     </row>
-    <row r="243" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="243" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="16"/>
@@ -16481,7 +16575,7 @@
       <c r="F243" s="16"/>
       <c r="G243" s="16"/>
     </row>
-    <row r="244" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="244" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="16"/>
@@ -16490,7 +16584,7 @@
       <c r="F244" s="16"/>
       <c r="G244" s="16"/>
     </row>
-    <row r="245" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="245" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="16"/>
@@ -16499,7 +16593,7 @@
       <c r="F245" s="16"/>
       <c r="G245" s="16"/>
     </row>
-    <row r="246" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="246" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="16"/>
@@ -16508,7 +16602,7 @@
       <c r="F246" s="16"/>
       <c r="G246" s="16"/>
     </row>
-    <row r="247" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="247" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="16"/>
@@ -16517,7 +16611,7 @@
       <c r="F247" s="16"/>
       <c r="G247" s="16"/>
     </row>
-    <row r="248" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="248" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="16"/>
@@ -16526,7 +16620,7 @@
       <c r="F248" s="16"/>
       <c r="G248" s="16"/>
     </row>
-    <row r="249" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="249" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="16"/>
@@ -16535,7 +16629,7 @@
       <c r="F249" s="16"/>
       <c r="G249" s="16"/>
     </row>
-    <row r="250" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="250" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="16"/>
@@ -16544,7 +16638,7 @@
       <c r="F250" s="16"/>
       <c r="G250" s="16"/>
     </row>
-    <row r="251" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="251" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="16"/>
@@ -16553,7 +16647,7 @@
       <c r="F251" s="16"/>
       <c r="G251" s="16"/>
     </row>
-    <row r="252" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="252" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="16"/>
@@ -16562,7 +16656,7 @@
       <c r="F252" s="16"/>
       <c r="G252" s="16"/>
     </row>
-    <row r="253" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="253" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="16"/>
@@ -16571,7 +16665,7 @@
       <c r="F253" s="16"/>
       <c r="G253" s="16"/>
     </row>
-    <row r="254" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="254" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="16"/>
@@ -16580,7 +16674,7 @@
       <c r="F254" s="16"/>
       <c r="G254" s="16"/>
     </row>
-    <row r="255" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="255" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="16"/>
@@ -16589,7 +16683,7 @@
       <c r="F255" s="16"/>
       <c r="G255" s="16"/>
     </row>
-    <row r="256" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="256" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="16"/>
@@ -16598,7 +16692,7 @@
       <c r="F256" s="16"/>
       <c r="G256" s="16"/>
     </row>
-    <row r="257" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="257" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="16"/>
@@ -16607,7 +16701,7 @@
       <c r="F257" s="16"/>
       <c r="G257" s="16"/>
     </row>
-    <row r="258" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="258" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="16"/>
@@ -16616,7 +16710,7 @@
       <c r="F258" s="16"/>
       <c r="G258" s="16"/>
     </row>
-    <row r="259" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="259" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="16"/>
@@ -16625,7 +16719,7 @@
       <c r="F259" s="16"/>
       <c r="G259" s="16"/>
     </row>
-    <row r="260" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="260" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="16"/>
@@ -16634,7 +16728,7 @@
       <c r="F260" s="16"/>
       <c r="G260" s="16"/>
     </row>
-    <row r="261" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="261" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="16"/>
@@ -16643,7 +16737,7 @@
       <c r="F261" s="16"/>
       <c r="G261" s="16"/>
     </row>
-    <row r="262" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="262" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="16"/>
@@ -16652,7 +16746,7 @@
       <c r="F262" s="16"/>
       <c r="G262" s="16"/>
     </row>
-    <row r="263" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="263" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="16"/>
@@ -16680,12 +16774,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="19.899999999999999" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="16.28515625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="20" customWidth="1"/>
-    <col min="7" max="8" width="16.28515625" style="20" customWidth="1"/>
-    <col min="9" max="16384" width="16.28515625" style="20"/>
+    <col min="1" max="5" width="16.26953125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="22.26953125" style="20" customWidth="1"/>
+    <col min="7" max="8" width="16.26953125" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="16.26953125" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1">
@@ -16736,7 +16830,7 @@
       </c>
       <c r="G3" s="30"/>
     </row>
-    <row r="4" spans="1:7" ht="20.45" customHeight="1">
+    <row r="4" spans="1:7" ht="20.5" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="28">
         <v>46225.302083333336</v>
@@ -16757,7 +16851,7 @@
         <v>0.17249999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20.45" customHeight="1">
+    <row r="5" spans="1:7" ht="20.5" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="28">
         <v>46225.322916666664</v>
@@ -16778,7 +16872,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="20.45" customHeight="1">
+    <row r="6" spans="1:7" ht="20.5" customHeight="1">
       <c r="A6" s="13"/>
       <c r="B6" s="28">
         <v>46225.34375</v>
@@ -16799,7 +16893,7 @@
         <v>0.19500000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="20.45" customHeight="1">
+    <row r="7" spans="1:7" ht="20.5" customHeight="1">
       <c r="A7" s="13"/>
       <c r="B7" s="28">
         <v>46225.364583333336</v>
@@ -16820,7 +16914,7 @@
         <v>0.16750000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="20.45" customHeight="1">
+    <row r="8" spans="1:7" ht="20.5" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="28">
         <v>46225.385416666664</v>
@@ -16841,7 +16935,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20.45" customHeight="1">
+    <row r="9" spans="1:7" ht="20.5" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="31">
         <v>46225.385416666664</v>
@@ -16854,7 +16948,7 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
     </row>
-    <row r="10" spans="1:7" ht="20.45" customHeight="1">
+    <row r="10" spans="1:7" ht="20.5" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="28">
         <v>46225.40625</v>
@@ -16875,7 +16969,7 @@
         <v>8.500000000000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.45" customHeight="1">
+    <row r="11" spans="1:7" ht="20.5" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="28">
         <v>46225.427083333336</v>
@@ -16896,7 +16990,7 @@
         <v>5.7500000000000051E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20.45" customHeight="1">
+    <row r="12" spans="1:7" ht="20.5" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="28">
         <v>46225.447916666664</v>
@@ -16917,7 +17011,7 @@
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20.45" customHeight="1">
+    <row r="13" spans="1:7" ht="20.5" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>46225.46875</v>
@@ -16938,7 +17032,7 @@
         <v>5.00000000000006E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20.45" customHeight="1">
+    <row r="14" spans="1:7" ht="20.5" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>46225.489583333336</v>
@@ -16959,7 +17053,7 @@
         <v>-1.4999999999999958E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.45" customHeight="1">
+    <row r="15" spans="1:7" ht="20.5" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="28">
         <v>46225.510416666664</v>
@@ -16980,7 +17074,7 @@
         <v>-2.4999999999999967E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="20.45" customHeight="1">
+    <row r="16" spans="1:7" ht="20.5" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="28">
         <v>46225.53125</v>
@@ -17001,7 +17095,7 @@
         <v>-3.2499999999999973E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="20.45" customHeight="1">
+    <row r="17" spans="1:7" ht="20.5" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="28">
         <v>46225.552083333336</v>
@@ -17022,7 +17116,7 @@
         <v>-3.2499999999999973E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.45" customHeight="1">
+    <row r="18" spans="1:7" ht="20.5" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="28">
         <v>46225.572916666664</v>
@@ -17043,7 +17137,7 @@
         <v>-2.9999999999999971E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20.45" customHeight="1">
+    <row r="19" spans="1:7" ht="20.5" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="28">
         <v>46225.59375</v>
@@ -17064,7 +17158,7 @@
         <v>-1.9999999999999962E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.45" customHeight="1">
+    <row r="20" spans="1:7" ht="20.5" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="28">
         <v>46225.614583333336</v>
@@ -17085,7 +17179,7 @@
         <v>-5.0000000000000044E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="20.45" customHeight="1">
+    <row r="21" spans="1:7" ht="20.5" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="28">
         <v>46225.635416666664</v>
@@ -17106,7 +17200,7 @@
         <v>7.5000000000000067E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.45" customHeight="1">
+    <row r="22" spans="1:7" ht="20.5" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="28">
         <v>46225.65625</v>
@@ -17127,7 +17221,7 @@
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="20.45" customHeight="1">
+    <row r="23" spans="1:7" ht="20.5" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="28">
         <v>46225.677083333336</v>
@@ -17148,7 +17242,7 @@
         <v>6.5000000000000058E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.45" customHeight="1">
+    <row r="24" spans="1:7" ht="20.5" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="28">
         <v>46225.697916666664</v>
@@ -17169,7 +17263,7 @@
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.45" customHeight="1">
+    <row r="25" spans="1:7" ht="20.5" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="28">
         <v>46225.697916666664</v>
@@ -17182,7 +17276,7 @@
       <c r="F25" s="30"/>
       <c r="G25" s="30"/>
     </row>
-    <row r="26" spans="1:7" ht="20.45" customHeight="1">
+    <row r="26" spans="1:7" ht="20.5" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="28">
         <v>46225.71875</v>
@@ -17203,7 +17297,7 @@
         <v>0.11000000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="20.45" customHeight="1">
+    <row r="27" spans="1:7" ht="20.5" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="28">
         <v>46225.739583333336</v>
@@ -17224,7 +17318,7 @@
         <v>0.15750000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.45" customHeight="1">
+    <row r="28" spans="1:7" ht="20.5" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="28">
         <v>46225.760416666664</v>
@@ -17245,7 +17339,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="20.45" customHeight="1">
+    <row r="29" spans="1:7" ht="20.5" customHeight="1">
       <c r="A29" s="32" t="s">
         <v>21</v>
       </c>
@@ -17260,7 +17354,7 @@
       <c r="F29" s="30"/>
       <c r="G29" s="30"/>
     </row>
-    <row r="30" spans="1:7" ht="20.45" customHeight="1">
+    <row r="30" spans="1:7" ht="20.5" customHeight="1">
       <c r="A30" s="32" t="s">
         <v>22</v>
       </c>
@@ -17275,7 +17369,7 @@
       <c r="F30" s="30"/>
       <c r="G30" s="30"/>
     </row>
-    <row r="31" spans="1:7" ht="20.45" customHeight="1">
+    <row r="31" spans="1:7" ht="20.5" customHeight="1">
       <c r="A31" s="34" t="s">
         <v>23</v>
       </c>
@@ -17291,7 +17385,7 @@
         <v>1.5475000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="20.45" customHeight="1">
+    <row r="32" spans="1:7" ht="20.5" customHeight="1">
       <c r="A32" s="32" t="s">
         <v>24</v>
       </c>
@@ -17333,10 +17427,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="19.899999999999999" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
-    <col min="1" max="10" width="16.28515625" style="35" customWidth="1"/>
-    <col min="11" max="16384" width="16.28515625" style="35"/>
+    <col min="1" max="10" width="16.26953125" style="35" customWidth="1"/>
+    <col min="11" max="16384" width="16.26953125" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
@@ -17402,7 +17496,7 @@
       </c>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:9" ht="20.45" customHeight="1">
+    <row r="4" spans="1:9" ht="20.5" customHeight="1">
       <c r="A4" s="28">
         <v>46225.302083333336</v>
       </c>
@@ -17426,7 +17520,7 @@
         <v>2.4999999999999994E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.45" customHeight="1">
+    <row r="5" spans="1:9" ht="20.5" customHeight="1">
       <c r="A5" s="28">
         <v>46225.322916666664</v>
       </c>
@@ -17450,7 +17544,7 @@
         <v>7.9999999999999988E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A6" s="28">
         <v>46225.34375</v>
       </c>
@@ -17474,7 +17568,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1">
       <c r="A7" s="28">
         <v>46225.364583333336</v>
       </c>
@@ -17498,7 +17592,7 @@
         <v>0.19749999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="20.45" customHeight="1">
+    <row r="8" spans="1:9" ht="20.5" customHeight="1">
       <c r="A8" s="28">
         <v>46225.385416666664</v>
       </c>
@@ -17522,7 +17616,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.45" customHeight="1">
+    <row r="9" spans="1:9" ht="20.5" customHeight="1">
       <c r="A9" s="31">
         <v>46225.385416666664</v>
       </c>
@@ -17540,7 +17634,7 @@
       </c>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="20.45" customHeight="1">
+    <row r="10" spans="1:9" ht="20.5" customHeight="1">
       <c r="A10" s="28">
         <v>46225.40625</v>
       </c>
@@ -17564,7 +17658,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.45" customHeight="1">
+    <row r="11" spans="1:9" ht="20.5" customHeight="1">
       <c r="A11" s="28">
         <v>46225.427083333336</v>
       </c>
@@ -17588,7 +17682,7 @@
         <v>0.35499999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.45" customHeight="1">
+    <row r="12" spans="1:9" ht="20.5" customHeight="1">
       <c r="A12" s="28">
         <v>46225.447916666664</v>
       </c>
@@ -17612,7 +17706,7 @@
         <v>0.39750000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.45" customHeight="1">
+    <row r="13" spans="1:9" ht="20.5" customHeight="1">
       <c r="A13" s="28">
         <v>46225.46875</v>
       </c>
@@ -17636,7 +17730,7 @@
         <v>0.4325</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.45" customHeight="1">
+    <row r="14" spans="1:9" ht="20.5" customHeight="1">
       <c r="A14" s="28">
         <v>46225.489583333336</v>
       </c>
@@ -17660,7 +17754,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="20.45" customHeight="1">
+    <row r="15" spans="1:9" ht="20.5" customHeight="1">
       <c r="A15" s="28">
         <v>46225.510416666664</v>
       </c>
@@ -17684,7 +17778,7 @@
         <v>0.47499999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20.45" customHeight="1">
+    <row r="16" spans="1:9" ht="20.5" customHeight="1">
       <c r="A16" s="28">
         <v>46225.53125</v>
       </c>
@@ -17708,7 +17802,7 @@
         <v>0.48499999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="20.45" customHeight="1">
+    <row r="17" spans="1:9" ht="20.5" customHeight="1">
       <c r="A17" s="28">
         <v>46225.552083333336</v>
       </c>
@@ -17732,7 +17826,7 @@
         <v>0.48749999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="20.45" customHeight="1">
+    <row r="18" spans="1:9" ht="20.5" customHeight="1">
       <c r="A18" s="28">
         <v>46225.572916666664</v>
       </c>
@@ -17756,7 +17850,7 @@
         <v>0.48249999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="20.45" customHeight="1">
+    <row r="19" spans="1:9" ht="20.5" customHeight="1">
       <c r="A19" s="28">
         <v>46225.59375</v>
       </c>
@@ -17780,7 +17874,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="20.45" customHeight="1">
+    <row r="20" spans="1:9" ht="20.5" customHeight="1">
       <c r="A20" s="28">
         <v>46225.614583333336</v>
       </c>
@@ -17804,7 +17898,7 @@
         <v>0.45000000000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="20.45" customHeight="1">
+    <row r="21" spans="1:9" ht="20.5" customHeight="1">
       <c r="A21" s="28">
         <v>46225.635416666664</v>
       </c>
@@ -17828,7 +17922,7 @@
         <v>0.42750000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="20.45" customHeight="1">
+    <row r="22" spans="1:9" ht="20.5" customHeight="1">
       <c r="A22" s="28">
         <v>46225.65625</v>
       </c>
@@ -17852,7 +17946,7 @@
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="20.45" customHeight="1">
+    <row r="23" spans="1:9" ht="20.5" customHeight="1">
       <c r="A23" s="28">
         <v>46225.677083333336</v>
       </c>
@@ -17876,7 +17970,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="20.45" customHeight="1">
+    <row r="24" spans="1:9" ht="20.5" customHeight="1">
       <c r="A24" s="28">
         <v>46225.697916666664</v>
       </c>
@@ -17900,7 +17994,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="20.45" customHeight="1">
+    <row r="25" spans="1:9" ht="20.5" customHeight="1">
       <c r="A25" s="28">
         <v>46225.697916666664</v>
       </c>
@@ -17918,7 +18012,7 @@
       </c>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" ht="20.45" customHeight="1">
+    <row r="26" spans="1:9" ht="20.5" customHeight="1">
       <c r="A26" s="28">
         <v>46225.71875</v>
       </c>
@@ -17942,7 +18036,7 @@
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="20.45" customHeight="1">
+    <row r="27" spans="1:9" ht="20.5" customHeight="1">
       <c r="A27" s="28">
         <v>46225.739583333336</v>
       </c>
@@ -17966,7 +18060,7 @@
         <v>0.21499999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="20.45" customHeight="1">
+    <row r="28" spans="1:9" ht="20.5" customHeight="1">
       <c r="A28" s="28">
         <v>46225.760416666664</v>
       </c>
@@ -17990,7 +18084,7 @@
         <v>0.15249999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="20.45" customHeight="1">
+    <row r="29" spans="1:9" ht="20.5" customHeight="1">
       <c r="A29" s="28">
         <v>0.78125</v>
       </c>
@@ -18003,7 +18097,7 @@
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
     </row>
-    <row r="30" spans="1:9" ht="20.45" customHeight="1">
+    <row r="30" spans="1:9" ht="20.5" customHeight="1">
       <c r="A30" s="28">
         <v>0.80208333333333337</v>
       </c>
@@ -18016,7 +18110,7 @@
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
     </row>
-    <row r="31" spans="1:9" ht="20.45" customHeight="1">
+    <row r="31" spans="1:9" ht="20.5" customHeight="1">
       <c r="A31" s="33"/>
       <c r="B31" s="33"/>
       <c r="C31" s="15" cm="1">
@@ -18057,23 +18151,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="42" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" style="42" customWidth="1"/>
     <col min="2" max="2" width="13" style="42" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="42" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="42"/>
+    <col min="3" max="3" width="11.1796875" style="42" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.75">
+    <row r="1" spans="1:5" ht="24">
       <c r="A1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="40" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>35</v>
       </c>
       <c r="D1" s="40" t="s">
         <v>33</v>
@@ -18511,7 +18605,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="42">
         <f>(B3+B2)/2*0.5</f>
@@ -18864,7 +18958,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" s="42">
         <f>SUM(B29:B53)</f>

--- a/Voltage_discharge.xlsx
+++ b/Voltage_discharge.xlsx
@@ -606,7 +606,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999831"/>
+          <c:h val="0.8103369999999982"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1879,11 +1879,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="129728896"/>
-        <c:axId val="129731968"/>
+        <c:axId val="169767296"/>
+        <c:axId val="169770368"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="129728896"/>
+        <c:axId val="169767296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1915,14 +1915,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129731968"/>
+        <c:crossAx val="169770368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="129731968"/>
+        <c:axId val="169770368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -1965,7 +1965,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129728896"/>
+        <c:crossAx val="169767296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -1989,7 +1989,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000212E-2"/>
+          <c:h val="6.4066700000000226E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -2029,7 +2029,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000167" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000167" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2049,7 +2049,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999831"/>
+          <c:h val="0.8103369999999982"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -3488,11 +3488,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="129538304"/>
-        <c:axId val="129544192"/>
+        <c:axId val="169576704"/>
+        <c:axId val="169582592"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="129538304"/>
+        <c:axId val="169576704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3524,14 +3524,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129544192"/>
+        <c:crossAx val="169582592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="129544192"/>
+        <c:axId val="169582592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -3574,7 +3574,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129538304"/>
+        <c:crossAx val="169576704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -3598,7 +3598,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000212E-2"/>
+          <c:h val="6.4066700000000226E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -3638,7 +3638,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000167" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000167" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -3655,10 +3655,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.1082899999999994E-2"/>
+          <c:x val="9.1082900000000008E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89393599999999951"/>
-          <c:h val="0.81033699999999831"/>
+          <c:h val="0.8103369999999982"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -4600,11 +4600,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="129682816"/>
-        <c:axId val="129684608"/>
+        <c:axId val="169696640"/>
+        <c:axId val="169702528"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="129682816"/>
+        <c:axId val="169696640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4636,14 +4636,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129684608"/>
+        <c:crossAx val="169702528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="3"/>
         <c:minorUnit val="1.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="129684608"/>
+        <c:axId val="169702528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -4685,7 +4685,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129682816"/>
+        <c:crossAx val="169696640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -4709,7 +4709,7 @@
           <c:x val="7.5226400000000082E-2"/>
           <c:y val="0"/>
           <c:w val="0.88994100000000065"/>
-          <c:h val="6.4066700000000212E-2"/>
+          <c:h val="6.4066700000000226E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -4749,7 +4749,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000167" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000167" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -4769,7 +4769,7 @@
           <c:x val="9.1001100000000015E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.89403199999999949"/>
-          <c:h val="0.81033699999999831"/>
+          <c:h val="0.8103369999999982"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6042,11 +6042,11 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="129725568"/>
-        <c:axId val="129727104"/>
+        <c:axId val="169755776"/>
+        <c:axId val="169757312"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="129725568"/>
+        <c:axId val="169755776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6078,14 +6078,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129727104"/>
+        <c:crossAx val="169757312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
         <c:minorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="129727104"/>
+        <c:axId val="169757312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="13"/>
@@ -6128,7 +6128,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129725568"/>
+        <c:crossAx val="169755776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -6188,7 +6188,7 @@
           <c:x val="7.5607700000000014E-2"/>
           <c:y val="0"/>
           <c:w val="0.88914199999999999"/>
-          <c:h val="6.4066700000000212E-2"/>
+          <c:h val="6.4066700000000226E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -6232,7 +6232,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000167" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000167" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -6249,10 +6249,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.4312400000000297E-2"/>
+          <c:x val="6.4312400000000325E-2"/>
           <c:y val="0.12368000000000012"/>
           <c:w val="0.88765000000000005"/>
-          <c:h val="0.81033699999999831"/>
+          <c:h val="0.8103369999999982"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6460,11 +6460,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="129903616"/>
-        <c:axId val="129909504"/>
+        <c:axId val="169815040"/>
+        <c:axId val="169816832"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="129903616"/>
+        <c:axId val="169815040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="806395000"/>
@@ -6497,12 +6497,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129909504"/>
+        <c:crossAx val="169816832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="129909504"/>
+        <c:axId val="169816832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6543,7 +6543,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="129903616"/>
+        <c:crossAx val="169815040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.2"/>
@@ -6567,7 +6567,7 @@
           <c:x val="4.0081200000000004E-2"/>
           <c:y val="0"/>
           <c:w val="0.9"/>
-          <c:h val="6.4066700000000212E-2"/>
+          <c:h val="6.4066700000000226E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -6607,7 +6607,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000155" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000155" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000167" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000167" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -6640,7 +6640,7 @@
                 <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>Current Production</a:t>
+              <a:t>Current Generation</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0">
@@ -7245,11 +7245,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="130158976"/>
-        <c:axId val="130160512"/>
+        <c:axId val="170063360"/>
+        <c:axId val="170064896"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="130158976"/>
+        <c:axId val="170063360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7273,14 +7273,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="130160512"/>
+        <c:crossAx val="170064896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="130160512"/>
+        <c:axId val="170064896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7335,7 +7335,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="130158976"/>
+        <c:crossAx val="170063360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7374,7 +7374,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000111" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000111" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
